--- a/excel_templates/proteomics_manifest_template.xlsx
+++ b/excel_templates/proteomics_manifest_template.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>PT007</t>
+          <t>P_5P2QIUH2</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>SM8182-86886</t>
+          <t>S_0000012</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>AL54774975_T_Prot</t>
+          <t>AL_0000025_T_Prot</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>PID1899</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -654,7 +654,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8182-86886</t>
+          <t>7316-11566</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -683,7 +683,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54774975_T_Prot</t>
+          <t>1549608_T_Prot</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>MODEL-PARENT-001</t>
+          <t>CNMC-XD760</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>MODEL-GM-001</t>
+          <t>CNMC-XD760-mCherry-Luciferase</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -1424,7 +1424,11 @@
           <t>Name of the type of experiment being performed</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>"Whole Cell Proteomics", "Phospho-Proteomics"</t>
+        </is>
+      </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1432,7 +1436,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Proteomics</t>
+          <t>Whole Cell Proteomics</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -1755,7 +1759,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>impact trial</t>
+          <t>RBT</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2124,7 +2128,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="8">
+  <dataValidations count="9">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$6</formula1>
     </dataValidation>
@@ -2143,11 +2147,14 @@
     <dataValidation sqref="AB2:AB1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$F$2:$F$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AR2:AR1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AF2:AF1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$G$2:$G$3</formula1>
     </dataValidation>
+    <dataValidation sqref="AR2:AR1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$H$2:$H$3</formula1>
+    </dataValidation>
     <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$H$2:$H$2</formula1>
+      <formula1>'Lists'!$I$2:$I$2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2160,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2196,10 +2203,15 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>experimental_strategy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>organism</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>host_organism</t>
         </is>
@@ -2238,10 +2250,15 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Whole Cell Proteomics</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
@@ -2279,6 +2296,11 @@
         </is>
       </c>
       <c r="G3" t="inlineStr">
+        <is>
+          <t>Phospho-Proteomics</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>

--- a/excel_templates/proteomics_manifest_template.xlsx
+++ b/excel_templates/proteomics_manifest_template.xlsx
@@ -1850,7 +1850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS1"/>
+  <dimension ref="A1:AT1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1898,6 +1898,7 @@
     <col width="24" customWidth="1" min="43" max="43"/>
     <col width="24" customWidth="1" min="44" max="44"/>
     <col width="24" customWidth="1" min="45" max="45"/>
+    <col width="24" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2013,115 +2014,120 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>file_platform</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>sequencing_batch</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>proteomics_experiment</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>file_name</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>file_format</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>file_size</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>file_hash_type</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>file_hash_value</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>sequencing_center</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
+          <t>instrument_platform</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
           <t>experimental_strategy</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>acquisition_type</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>ion_fragmentation</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>enrichment_approach</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>quantification_technique</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>quantification_labeling_method</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>quantification_label_id</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>chromatography_approach</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>fractionation_approach</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>fraction_number</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>PI_name</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>organism</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>host_organism</t>
         </is>
@@ -2138,22 +2144,22 @@
     <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$C$2:$C$20</formula1>
     </dataValidation>
-    <dataValidation sqref="X2:X1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Y2:Y1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$D$2:$D$8</formula1>
     </dataValidation>
-    <dataValidation sqref="Z2:Z1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AA2:AA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$E$2:$E$26</formula1>
     </dataValidation>
-    <dataValidation sqref="AB2:AB1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AC2:AC1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$F$2:$F$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AF2:AF1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG2:AG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$G$2:$G$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AR2:AR1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$H$2:$H$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AT2:AT1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$I$2:$I$2</formula1>
     </dataValidation>
   </dataValidations>

--- a/excel_templates/proteomics_manifest_template.xlsx
+++ b/excel_templates/proteomics_manifest_template.xlsx
@@ -2014,7 +2014,7 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>file_platform</t>
+          <t>file_source_platform</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">

--- a/excel_templates/proteomics_manifest_template.xlsx
+++ b/excel_templates/proteomics_manifest_template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>SMB directory path on the L Drive for the source data</t>
+          <t>SMB directory path on the L Drive for the source data. Required when file_source_platform is local_drive or bti_aws_and_local_drive</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>S3 URI for the submitted data location</t>
+          <t>S3 URI for the submitted data location. Required when file_source_platform is bti_aws or bti_aws_and_local_drive</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -1138,20 +1138,24 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>sequencing_batch</t>
+          <t>file_source_platform</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Sequencing batch identifier</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr"/>
+          <t>Source platform where files are stored and from which they are harmonized</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>"bti_aws", "local_drive", "bti_aws_and_local_drive", "cgc", "kids_first", "sra", "synapse"</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1159,7 +1163,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30-XXXXXXXX</t>
+          <t>bti_aws</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -1167,24 +1171,20 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>proteomics_experiment</t>
+          <t>sequencing_batch</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>The type of omics experiment that the sample was subject to. This will be a proteomics-based data, by default, but this should specify the type of proteomics data.</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>"Proteome", "Ubiquitylome", "Phosphoproteome", "Acetylome", "Glycoproteome", "Metabolome", "Lipidome"</t>
-        </is>
-      </c>
+          <t>Sequencing batch identifier</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Metabolome</t>
+          <t>30-XXXXXXXX</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -1200,7 +1200,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>file_name</t>
+          <t>proteomics_experiment</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1210,10 +1210,14 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Name of the file</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr"/>
+          <t>The type of omics experiment that the sample was subject to. This will be a proteomics-based data, by default, but this should specify the type of proteomics data.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>"Proteome", "Ubiquitylome", "Phosphoproteome", "Acetylome", "Glycoproteome", "Metabolome", "Lipidome"</t>
+        </is>
+      </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1221,7 +1225,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>NCI-11Plex-13-F12A-z11358.mzML</t>
+          <t>Metabolome</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1229,7 +1233,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>file_format</t>
+          <t>file_name</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1239,14 +1243,10 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Format of the file</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "raw"</t>
-        </is>
-      </c>
+          <t>Name of the file</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>mzML</t>
+          <t>NCI-11Plex-13-F12A-z11358.mzML</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1262,7 +1262,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>file_size</t>
+          <t>file_format</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1272,18 +1272,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Reported file size in bytes</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr"/>
+          <t>Format of the file</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "raw"</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>235000</t>
+          <t>mzML</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1291,7 +1295,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>file_hash_type</t>
+          <t>file_size</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1301,22 +1305,18 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Hash algorithm used to generate file hash</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>"MD5", "SHA1", "SHA256", "SHA512", "ETag"</t>
-        </is>
-      </c>
+          <t>Reported file size in bytes</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>MD5</t>
+          <t>235000</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1324,7 +1324,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>file_hash_value</t>
+          <t>file_hash_type</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1334,10 +1334,14 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Full has value of the file</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
+          <t>Hash algorithm used to generate file hash</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>"MD5", "SHA1", "SHA256", "SHA512", "ETag"</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1345,7 +1349,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>938c2cc0dcc05f2b68c4287040cfcf71</t>
+          <t>MD5</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1353,17 +1357,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>sequencing_center</t>
+          <t>file_hash_value</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Name of the center generating sequencing data</t>
+          <t>Full has value of the file</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
@@ -1374,7 +1378,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Harvard Med School</t>
+          <t>938c2cc0dcc05f2b68c4287040cfcf71</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1382,17 +1386,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>sequencing_center</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Name of the platform used to obtain data</t>
+          <t>Name of the center generating sequencing data</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
@@ -1403,7 +1407,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Orbitrap Fusion Lumos</t>
+          <t>Harvard Med School</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -1411,7 +1415,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>experimental_strategy</t>
+          <t>instrument_platform</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1421,14 +1425,10 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Name of the type of experiment being performed</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>"Whole Cell Proteomics", "Phospho-Proteomics"</t>
-        </is>
-      </c>
+          <t>Name of the platform used to obtain data</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Whole Cell Proteomics</t>
+          <t>Orbitrap Fusion Lumos</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -1444,7 +1444,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>acquisition_type</t>
+          <t>experimental_strategy</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1454,10 +1454,14 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Data acquisition type</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr"/>
+          <t>Name of the type of experiment being performed</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>"Whole Cell Proteomics", "Phospho-Proteomics"</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1465,7 +1469,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>DDA</t>
+          <t>Whole Cell Proteomics</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -1473,7 +1477,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ion_fragmentation</t>
+          <t>acquisition_type</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1483,7 +1487,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Reporter ion MS level</t>
+          <t>Data acquisition type</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
@@ -1494,7 +1498,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>MS2</t>
+          <t>DDA</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -1502,7 +1506,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>enrichment_approach</t>
+          <t>ion_fragmentation</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1512,7 +1516,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Enrichment method used for phospho, ubiquitin, acetyl, or other enrichment</t>
+          <t>Reporter ion MS level</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
@@ -1523,7 +1527,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>metabolome</t>
+          <t>MS2</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -1531,7 +1535,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>quantification_technique</t>
+          <t>enrichment_approach</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1541,7 +1545,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Approach used for peptide quantification</t>
+          <t>Enrichment method used for phospho, ubiquitin, acetyl, or other enrichment</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
@@ -1552,7 +1556,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Stable isotopic labeling</t>
+          <t>metabolome</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -1560,7 +1564,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>quantification_labeling_method</t>
+          <t>quantification_technique</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1570,7 +1574,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Method used for labeling or NA if label-free</t>
+          <t>Approach used for peptide quantification</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
@@ -1581,7 +1585,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>L-Lysine SILAC</t>
+          <t>Stable isotopic labeling</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1589,7 +1593,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>quantification_label_id</t>
+          <t>quantification_labeling_method</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1599,7 +1603,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Specific label used or NA if label-free</t>
+          <t>Method used for labeling or NA if label-free</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
@@ -1610,7 +1614,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>127N</t>
+          <t>L-Lysine SILAC</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -1618,7 +1622,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>chromatography_approach</t>
+          <t>quantification_label_id</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1628,7 +1632,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Column type used for liquid chromatography</t>
+          <t>Specific label used or NA if label-free</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
@@ -1639,7 +1643,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>127N</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -1647,7 +1651,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>fractionation_approach</t>
+          <t>chromatography_approach</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1657,7 +1661,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Method used to fractionate sample.</t>
+          <t>Column type used for liquid chromatography</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
@@ -1668,7 +1672,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>reverse-phase HPLC</t>
+          <t>C18</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -1676,7 +1680,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>fraction_number</t>
+          <t>fractionation_approach</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1686,18 +1690,18 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Number of fractions generated for sample.</t>
+          <t>Method used to fractionate sample.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>reverse-phase HPLC</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -1705,7 +1709,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>PI_name</t>
+          <t>fraction_number</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1715,30 +1719,26 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Principal Investigator of the project</t>
+          <t>Number of fractions generated for sample.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Fonseca</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>PI_name</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Short name of the project</t>
+          <t>Principal Investigator of the project</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>RBT</t>
+          <t>Fonseca</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>organism</t>
+          <t>project</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1781,14 +1781,10 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Binomial name of organism with full genus name</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>"Homo sapiens", "Mus musculus"</t>
-        </is>
-      </c>
+          <t>Short name of the project</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1796,50 +1792,87 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr"/>
+          <t>RBT</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>organism</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Binomial name of organism with full genus name</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>"Homo sapiens", "Mus musculus"</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
           <t>host_organism</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Host organism binomial name when the sequenced sample is a xenograft. Required when compisition is "Patient Derived Xenograft" or "Xenograft"</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>"Mus musculus"</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G46"/>
+  <autoFilter ref="A1:G47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2134,7 +2167,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="9">
+  <dataValidations count="10">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$6</formula1>
     </dataValidation>
@@ -2144,23 +2177,26 @@
     <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$C$2:$C$20</formula1>
     </dataValidation>
-    <dataValidation sqref="Y2:Y1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="W2:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$D$2:$D$8</formula1>
     </dataValidation>
+    <dataValidation sqref="Y2:Y1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$E$2:$E$8</formula1>
+    </dataValidation>
     <dataValidation sqref="AA2:AA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$E$2:$E$26</formula1>
+      <formula1>'Lists'!$F$2:$F$26</formula1>
     </dataValidation>
     <dataValidation sqref="AC2:AC1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$F$2:$F$6</formula1>
+      <formula1>'Lists'!$G$2:$G$6</formula1>
     </dataValidation>
     <dataValidation sqref="AG2:AG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$G$2:$G$3</formula1>
+      <formula1>'Lists'!$H$2:$H$3</formula1>
     </dataValidation>
     <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$H$2:$H$3</formula1>
+      <formula1>'Lists'!$I$2:$I$3</formula1>
     </dataValidation>
     <dataValidation sqref="AT2:AT1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$I$2:$I$2</formula1>
+      <formula1>'Lists'!$J$2:$J$2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2173,7 +2209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2194,30 +2230,35 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>file_source_platform</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>proteomics_experiment</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>file_format</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>file_hash_type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>experimental_strategy</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>organism</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>host_organism</t>
         </is>
@@ -2241,30 +2282,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>bti_aws</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Proteome</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>FASTQ</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>MD5</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Whole Cell Proteomics</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
@@ -2288,25 +2334,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>local_drive</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Ubiquitylome</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>BAM</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>SHA1</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Phospho-Proteomics</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
@@ -2330,15 +2381,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>bti_aws_and_local_drive</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Phosphoproteome</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>BAI</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>SHA256</t>
         </is>
@@ -2362,15 +2418,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>cgc</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Acetylome</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>CRAM</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>SHA512</t>
         </is>
@@ -2394,15 +2455,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>kids_first</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Glycoproteome</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>CRAI</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>ETag</t>
         </is>
@@ -2421,10 +2487,15 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>sra</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Metabolome</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>GVCF</t>
         </is>
@@ -2443,10 +2514,15 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>synapse</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Lipidome</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>VCF</t>
         </is>
@@ -2463,7 +2539,7 @@
           <t>Patient Derived Organoid</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>TBI</t>
         </is>
@@ -2480,7 +2556,7 @@
           <t>Peripheral Blood Mononuclear Cells</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>MAF</t>
         </is>
@@ -2497,7 +2573,7 @@
           <t>Peripheral Whole Blood</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -2514,7 +2590,7 @@
           <t>Saliva</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
@@ -2531,7 +2607,7 @@
           <t>Solid Tissue</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>DCM</t>
         </is>
@@ -2548,7 +2624,7 @@
           <t>Umbilical Cord Blood</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>IDAT</t>
         </is>
@@ -2560,7 +2636,7 @@
           <t>Patient-Derived T Cells</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>SVS</t>
         </is>
@@ -2572,7 +2648,7 @@
           <t>Modified T Cells</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>GPR</t>
         </is>
@@ -2584,7 +2660,7 @@
           <t>Patient-Derived Primary Cells</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>CNS</t>
         </is>
@@ -2596,7 +2672,7 @@
           <t>iPSC-Derived Organoid</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>TXT</t>
         </is>
@@ -2608,7 +2684,7 @@
           <t>Cerebrospinal Fluid</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>PNG</t>
         </is>
@@ -2620,49 +2696,49 @@
           <t>Embryonic Stem Cell Derived Cell Line</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>PED</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>SEG</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>TAR</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>TSV</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>mzML</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>raw</t>
         </is>

--- a/excel_templates/proteomics_manifest_template.xlsx
+++ b/excel_templates/proteomics_manifest_template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1871,8 +1871,41 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>reported_gender</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Reported gender of the participant. Required when organism is "Homo sapiens"</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>"Female", "Male", "Not Reported"</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G47"/>
+  <autoFilter ref="A1:G48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1883,7 +1916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT1"/>
+  <dimension ref="A1:AU1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1932,6 +1965,7 @@
     <col width="24" customWidth="1" min="44" max="44"/>
     <col width="24" customWidth="1" min="45" max="45"/>
     <col width="24" customWidth="1" min="46" max="46"/>
+    <col width="24" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2165,9 +2199,14 @@
           <t>host_organism</t>
         </is>
       </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>reported_gender</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="10">
+  <dataValidations count="11">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$6</formula1>
     </dataValidation>
@@ -2198,6 +2237,9 @@
     <dataValidation sqref="AT2:AT1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$J$2:$J$2</formula1>
     </dataValidation>
+    <dataValidation sqref="AU2:AU1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$K$2:$K$4</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2209,7 +2251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2263,6 +2305,11 @@
           <t>host_organism</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>reported_gender</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2315,6 +2362,11 @@
           <t>Mus musculus</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2362,6 +2414,11 @@
           <t>Mus musculus</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2397,6 +2454,11 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>SHA256</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Not Reported</t>
         </is>
       </c>
     </row>
